--- a/results/components/gene_names/p6s4.xlsx
+++ b/results/components/gene_names/p6s4.xlsx
@@ -22,22 +22,22 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Psn</t>
-  </si>
-  <si>
-    <t>Ark</t>
-  </si>
-  <si>
-    <t>bib</t>
-  </si>
-  <si>
-    <t>noc</t>
-  </si>
-  <si>
-    <t>Akt1</t>
-  </si>
-  <si>
-    <t>Rack1</t>
+    <t>Ef1gamma</t>
+  </si>
+  <si>
+    <t>tin</t>
+  </si>
+  <si>
+    <t>Mmp1</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>Dif</t>
+  </si>
+  <si>
+    <t>Rca1</t>
   </si>
 </sst>
 </file>

--- a/results/components/gene_names/p6s4.xlsx
+++ b/results/components/gene_names/p6s4.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>gene1</t>
   </si>
@@ -22,22 +22,13 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Ef1gamma</t>
-  </si>
-  <si>
-    <t>tin</t>
-  </si>
-  <si>
-    <t>Mmp1</t>
-  </si>
-  <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t>Dif</t>
-  </si>
-  <si>
-    <t>Rca1</t>
+    <t>E(bx)</t>
+  </si>
+  <si>
+    <t>Su(z)12</t>
+  </si>
+  <si>
+    <t>trio</t>
   </si>
 </sst>
 </file>
@@ -369,7 +360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -393,15 +384,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
